--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484283_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484283_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1111</v>
+        <v>0.1728</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0688</v>
+        <v>0.2711</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1799</v>
+        <v>-0.0982</v>
       </c>
       <c r="G2" t="n">
         <v>-2.0319</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3872</v>
+        <v>-1.1033</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0289</v>
+        <v>-0.8267</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3583</v>
+        <v>-0.2766</v>
       </c>
       <c r="V2" t="n">
         <v>0.9639</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4105</v>
+        <v>0.0583</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7067</v>
+        <v>-1.3394</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2962</v>
+        <v>1.3977</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6879</v>
+        <v>-0.4766</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4587</v>
+        <v>-0.0987</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2292</v>
+        <v>-0.3778</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.6132</v>
+        <v>0.153</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0205</v>
+        <v>0.1253</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0276</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0747</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4792</v>
+        <v>-0.2241</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4045</v>
+        <v>-0.4054</v>
       </c>
       <c r="P3" t="n">
-        <v>0.586</v>
+        <v>2.1488</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
-        <v>0.586</v>
+        <v>3.1255</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3087</v>
+        <v>-0.8047</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0935</v>
+        <v>-0.5157</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2152</v>
+        <v>-0.2891</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.8092</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.8092</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6634</v>
+        <v>-0.3288</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.0066</v>
+        <v>-0.7067</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3433</v>
+        <v>0.3779</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4766</v>
+        <v>-0.6879</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0987</v>
+        <v>-0.4587</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3778</v>
+        <v>-0.2292</v>
       </c>
       <c r="J4" t="n">
-        <v>0.153</v>
+        <v>-0.6132</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1253</v>
+        <v>0.0205</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0276</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6294999999999999</v>
+        <v>-0.0747</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2241</v>
+        <v>-0.4792</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4054</v>
+        <v>0.4045</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1488</v>
+        <v>0.586</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1255</v>
+        <v>0.586</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5264</v>
+        <v>-0.227</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1829</v>
+        <v>-0.0935</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3435</v>
+        <v>-0.1335</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8092</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6984</v>
+        <v>-1.2797</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2227</v>
+        <v>-0.2224</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9211</v>
+        <v>-1.0573</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4837</v>
@@ -844,13 +844,13 @@
         <v>1.9534</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7924</v>
+        <v>0.2112</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5147</v>
+        <v>0.0696</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2778</v>
+        <v>0.1416</v>
       </c>
       <c r="V5" t="n">
         <v>-1.9839</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5035</v>
+        <v>-1.5229</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4131</v>
+        <v>0.312</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9166</v>
+        <v>-1.8349</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0229</v>
@@ -922,13 +922,13 @@
         <v>0.7814</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0353</v>
+        <v>0.0159</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2175</v>
+        <v>0.1164</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1822</v>
+        <v>-0.1005</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3205</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2</v>
+        <v>-1.8911</v>
       </c>
       <c r="E7" t="n">
         <v>-0.9607</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0393</v>
+        <v>-0.9304</v>
       </c>
       <c r="G7" t="n">
         <v>1.0857</v>
@@ -1000,13 +1000,13 @@
         <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4996</v>
+        <v>-0.3907</v>
       </c>
       <c r="T7" t="n">
         <v>-0.3026</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.197</v>
+        <v>-0.0881</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2186</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. RIVAS POMEROL</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.015</v>
+        <v>-2.4102</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2626</v>
+        <v>-1.381</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2476</v>
+        <v>-1.0291</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6173</v>
+        <v>-1.8403</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2865</v>
+        <v>-1.0172</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9039</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6372</v>
+        <v>-0.6116</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0025</v>
+        <v>-0.733</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.1214</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0198</v>
+        <v>-1.2287</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2891</v>
+        <v>-0.2842</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2692</v>
+        <v>-0.9445</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9938</v>
+        <v>-0.9643</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0815</v>
+        <v>-0.6244</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0877</v>
+        <v>-0.3399</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.2588</v>
+        <v>-0.3869</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.0511</v>
+        <v>0.8317</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2077</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7329</v>
+        <v>-2.7175</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7855</v>
+        <v>-2.3016</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9474</v>
+        <v>-0.4158</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8403</v>
+        <v>-1.4106</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0172</v>
+        <v>-0.8583</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.5523</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6116</v>
+        <v>-0.4515</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.733</v>
+        <v>-0.9785</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1214</v>
+        <v>0.527</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2287</v>
+        <v>-0.9591</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2842</v>
+        <v>0.1203</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9445</v>
+        <v>-1.0793</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.287</v>
+        <v>-0.3411</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0289</v>
+        <v>0.1033</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2582</v>
+        <v>-0.4444</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3869</v>
+        <v>0.011</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8317</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.017</v>
+        <v>-2.7954</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1386</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8785</v>
+        <v>-1.9602</v>
       </c>
       <c r="G10" t="n">
         <v>1.1867</v>
@@ -1234,13 +1234,13 @@
         <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2541</v>
+        <v>-1.0324</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0289</v>
+        <v>-0.7255</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2252</v>
+        <v>-0.3069</v>
       </c>
       <c r="V10" t="n">
         <v>-1.9729</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>A. RIVAS POMEROL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0619</v>
+        <v>-2.9813</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5644</v>
+        <v>-3.011</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4975</v>
+        <v>0.0297</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4106</v>
+        <v>0.6173</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8583</v>
+        <v>-0.2865</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5523</v>
+        <v>0.9039</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4515</v>
+        <v>0.6372</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9785</v>
+        <v>0.0025</v>
       </c>
       <c r="L11" t="n">
-        <v>0.527</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9591</v>
+        <v>-0.0198</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1203</v>
+        <v>-0.2891</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0793</v>
+        <v>0.2692</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9767</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6856</v>
+        <v>0.0275</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1594</v>
+        <v>0.3331</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5261</v>
+        <v>-0.3055</v>
       </c>
       <c r="V11" t="n">
-        <v>0.011</v>
+        <v>-2.2588</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-1.0511</v>
       </c>
       <c r="X11" t="n">
-        <v>0.011</v>
+        <v>-1.2077</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1696</v>
+        <v>-4.0001</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.907</v>
+        <v>-2.8464</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2626</v>
+        <v>-1.1537</v>
       </c>
       <c r="G12" t="n">
         <v>-4.3111</v>
@@ -1390,13 +1390,13 @@
         <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4445</v>
+        <v>-0.2751</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1983</v>
+        <v>0.2588</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6428</v>
+        <v>-0.5339</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.7737</v>
+        <v>-5.1588</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1891</v>
+        <v>-2.4924</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5847</v>
+        <v>-2.6664</v>
       </c>
       <c r="G13" t="n">
         <v>-0.3891</v>
@@ -1468,13 +1468,13 @@
         <v>0.3907</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5921</v>
+        <v>0.207</v>
       </c>
       <c r="T13" t="n">
-        <v>0.311</v>
+        <v>0.0076</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2811</v>
+        <v>0.1994</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4373</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-25.157</v>
+        <v>-24.8547</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.8166</v>
+        <v>-15.5137</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.340499999999999</v>
+        <v>-9.3407</v>
       </c>
       <c r="G14" t="n">
         <v>-9.764399999999998</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.347099999999999</v>
+        <v>-2.3471</v>
       </c>
       <c r="I14" t="n">
         <v>-7.4169</v>
@@ -1522,7 +1522,7 @@
         <v>-1.4974</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1551000000000001</v>
+        <v>-0.1551</v>
       </c>
       <c r="L14" t="n">
         <v>-1.3424</v>
@@ -1534,7 +1534,7 @@
         <v>-2.1923</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.074699999999999</v>
+        <v>-6.0747</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1546,13 +1546,13 @@
         <v>17.5807</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.979499999999999</v>
+        <v>-4.677</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.5021</v>
+        <v>-2.1996</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.4773</v>
+        <v>-2.4774</v>
       </c>
       <c r="V14" t="n">
         <v>-10.4132</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.9933</v>
+        <v>8.167400000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>5.3463</v>
+        <v>4.7396</v>
       </c>
       <c r="F15" t="n">
-        <v>3.647</v>
+        <v>3.4278</v>
       </c>
       <c r="G15" t="n">
         <v>0.9031</v>
@@ -1624,13 +1624,13 @@
         <v>2.3441</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6995</v>
+        <v>1.8736</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4914</v>
+        <v>0.8847</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2082</v>
+        <v>0.9889</v>
       </c>
       <c r="V15" t="n">
         <v>3.0466</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.8356</v>
+        <v>6.8536</v>
       </c>
       <c r="E16" t="n">
-        <v>5.0176</v>
+        <v>5.1187</v>
       </c>
       <c r="F16" t="n">
-        <v>1.818</v>
+        <v>1.7349</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2854</v>
@@ -1702,13 +1702,13 @@
         <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3719</v>
+        <v>0.39</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0221</v>
+        <v>0.1232</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3498</v>
+        <v>0.2667</v>
       </c>
       <c r="V16" t="n">
         <v>7.9211</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. CATANY BIGAS</t>
+          <t>E. ZUSTOVICH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.6052</v>
+        <v>5.1658</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6706</v>
+        <v>3.7847</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9347</v>
+        <v>1.3811</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2143</v>
+        <v>6.2852</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7524</v>
+        <v>2.4268</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9666</v>
+        <v>3.8585</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0349</v>
+        <v>5.6362</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2024</v>
+        <v>2.0466</v>
       </c>
       <c r="L17" t="n">
-        <v>3.2373</v>
+        <v>3.5896</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1794</v>
+        <v>0.649</v>
       </c>
       <c r="N17" t="n">
-        <v>0.45</v>
+        <v>0.3802</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2706</v>
+        <v>0.2688</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3441</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3441</v>
+        <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3241</v>
+        <v>0.5447</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6357</v>
+        <v>-0.0851</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3116</v>
+        <v>0.6299</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2772</v>
+        <v>-1.2735</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. ZUSTOVICH</t>
+          <t>G. CATANY BIGAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.3568</v>
+        <v>5.0267</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9758</v>
+        <v>2.4683</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3811</v>
+        <v>2.5584</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2852</v>
+        <v>2.2143</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4268</v>
+        <v>-0.7524</v>
       </c>
       <c r="I18" t="n">
-        <v>3.8585</v>
+        <v>2.9666</v>
       </c>
       <c r="J18" t="n">
-        <v>5.6362</v>
+        <v>2.0349</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0466</v>
+        <v>-1.2024</v>
       </c>
       <c r="L18" t="n">
-        <v>3.5896</v>
+        <v>3.2373</v>
       </c>
       <c r="M18" t="n">
-        <v>0.649</v>
+        <v>0.1794</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3802</v>
+        <v>0.45</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2688</v>
+        <v>-0.2706</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>2.3441</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5395</v>
+        <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2642</v>
+        <v>0.7456</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8941</v>
+        <v>0.4335</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6299</v>
+        <v>0.3121</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2735</v>
+        <v>-0.2772</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4373</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.9257</v>
+        <v>3.7762</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8636</v>
+        <v>1.4703</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0621</v>
+        <v>2.3058</v>
       </c>
       <c r="G19" t="n">
         <v>1.8159</v>
@@ -1936,13 +1936,13 @@
         <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2575</v>
+        <v>0.5929</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3631</v>
+        <v>0.2436</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1056</v>
+        <v>0.3494</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. ZICOVICH</t>
+          <t>B. HIDALGO GARRIGUES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2289</v>
+        <v>0.1498</v>
       </c>
       <c r="E20" t="n">
-        <v>1.062</v>
+        <v>-0.0352</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1669</v>
+        <v>0.185</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0674</v>
+        <v>0.1925</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-0.1312</v>
       </c>
       <c r="I20" t="n">
-        <v>2.0497</v>
+        <v>0.3237</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7427</v>
+        <v>-0.2719</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6332</v>
+        <v>-0.3262</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3758</v>
+        <v>0.0543</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3247</v>
+        <v>0.4644</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3492</v>
+        <v>0.1949</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.2694</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3568</v>
+        <v>-0.0743</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2727</v>
+        <v>0.2367</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08409999999999999</v>
+        <v>-0.311</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. JOVER SANS</t>
+          <t>A. BAUZA MEDINA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1412</v>
+        <v>0.1381</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3025</v>
+        <v>-2.8533</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1613</v>
+        <v>2.9913</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1428</v>
+        <v>1.7307</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2599</v>
+        <v>0.2745</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4027</v>
+        <v>1.4562</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9181</v>
+        <v>0.9365</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3492</v>
+        <v>0.2891</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2673</v>
+        <v>0.6475</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2247</v>
+        <v>0.7942</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0893</v>
+        <v>-0.0146</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1354</v>
+        <v>0.8087</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.586</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>0.701</v>
+        <v>0.0873</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6824</v>
+        <v>-0.1602</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0186</v>
+        <v>0.2475</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8865</v>
+        <v>0.6642</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8865</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. HIDALGO GARRIGUES</t>
+          <t>B. ZICOVICH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4726</v>
+        <v>-0.0584</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4397</v>
+        <v>-0.2525</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0329</v>
+        <v>0.1941</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1925</v>
+        <v>1.0674</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1312</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3237</v>
+        <v>2.0497</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2719</v>
+        <v>0.7427</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3262</v>
+        <v>-0.6332</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0543</v>
+        <v>1.3758</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4644</v>
+        <v>0.3247</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1949</v>
+        <v>-0.3492</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2694</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6966</v>
+        <v>1.0696</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1678</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5288</v>
+        <v>0.1113</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. PONS AVECILLAS</t>
+          <t>P. JOVER SANS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7164</v>
+        <v>-0.2954</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1222</v>
+        <v>-1.8081</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8385</v>
+        <v>1.5126</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8315</v>
+        <v>-1.1428</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3323</v>
+        <v>0.2599</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4992</v>
+        <v>-1.4027</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5518</v>
+        <v>-0.9181</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0819</v>
+        <v>0.3492</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.2673</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2797</v>
+        <v>-0.2247</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4142</v>
+        <v>-0.0893</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1344</v>
+        <v>-0.1354</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1721</v>
+        <v>-0.586</v>
       </c>
       <c r="Q23" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.5468</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="X23" t="n">
         <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.1721</v>
-      </c>
-      <c r="S23" t="n">
-        <v>-0.7796999999999999</v>
-      </c>
-      <c r="T23" t="n">
-        <v>-0.5447</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-0.235</v>
-      </c>
-      <c r="V23" t="n">
-        <v>-0.2772</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.2186</v>
-      </c>
-      <c r="X23" t="n">
-        <v>-1.4959</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. BAUZA MEDINA</t>
+          <t>S. PONS AVECILLAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7461</v>
+        <v>-0.4182</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3589</v>
+        <v>0.1222</v>
       </c>
       <c r="F24" t="n">
-        <v>2.6128</v>
+        <v>-0.5403</v>
       </c>
       <c r="G24" t="n">
-        <v>1.7307</v>
+        <v>-0.8315</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2745</v>
+        <v>-0.3323</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4562</v>
+        <v>-0.4992</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9365</v>
+        <v>-0.5518</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2891</v>
+        <v>0.0819</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6475</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7942</v>
+        <v>-0.2797</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0146</v>
+        <v>-0.4142</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8087</v>
+        <v>0.1344</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.3441</v>
+        <v>1.1721</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7968</v>
+        <v>-0.4815</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6657</v>
+        <v>-0.5447</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1311</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6642</v>
+        <v>-0.2772</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3869</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.7123</v>
+        <v>-2.0003</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.6162</v>
+        <v>-3.414</v>
       </c>
       <c r="F25" t="n">
-        <v>1.9039</v>
+        <v>1.4137</v>
       </c>
       <c r="G25" t="n">
         <v>-2.1851</v>
@@ -2404,13 +2404,13 @@
         <v>1.5627</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3211</v>
+        <v>1.0331</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0083</v>
+        <v>0.2106</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3127</v>
+        <v>0.8225</v>
       </c>
       <c r="V25" t="n">
         <v>1.4959</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>25.1569</v>
+        <v>26.5053</v>
       </c>
       <c r="E26" t="n">
-        <v>9.340799999999998</v>
+        <v>9.3407</v>
       </c>
       <c r="F26" t="n">
-        <v>15.8164</v>
+        <v>17.1644</v>
       </c>
       <c r="G26" t="n">
         <v>9.764299999999999</v>
@@ -2452,16 +2452,16 @@
         <v>2.3472</v>
       </c>
       <c r="I26" t="n">
-        <v>7.4171</v>
+        <v>7.417100000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>8.266999999999999</v>
+        <v>8.266999999999998</v>
       </c>
       <c r="K26" t="n">
-        <v>2.1923</v>
+        <v>2.192300000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>6.0749</v>
+        <v>6.074899999999999</v>
       </c>
       <c r="M26" t="n">
         <v>1.4973</v>
@@ -2473,7 +2473,7 @@
         <v>1.3422</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="Q26" t="n">
         <v>-17.5808</v>
@@ -2482,13 +2482,13 @@
         <v>17.5808</v>
       </c>
       <c r="S26" t="n">
-        <v>4.9796</v>
+        <v>6.327800000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4772</v>
+        <v>2.4774</v>
       </c>
       <c r="U26" t="n">
-        <v>2.5024</v>
+        <v>3.8504</v>
       </c>
       <c r="V26" t="n">
         <v>10.4133</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484283_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484283_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.7506</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.8092</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.9839</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.3708</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.011</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.9729</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.2077</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-16.1772</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-2.4373</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.3869</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484283_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-5.7641</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
